--- a/Data/Resultados_Cleveland/Resumen_CO_Congruente_vs_Incongruente_Generales.xlsx
+++ b/Data/Resultados_Cleveland/Resumen_CO_Congruente_vs_Incongruente_Generales.xlsx
@@ -485,16 +485,16 @@
         <v>425</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8541176470588235</v>
+        <v>0.1220168067226891</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7529411764705882</v>
+        <v>-0.107563025210084</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.607058823529412</v>
+        <v>-0.2295798319327731</v>
       </c>
       <c r="G2" t="n">
-        <v>7.347542033760345e-08</v>
+        <v>3.507727470097899e-08</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -517,16 +517,16 @@
         <v>1257</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9665871121718377</v>
+        <v>0.1380838731674054</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7764518695306285</v>
+        <v>-0.1109216956472327</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.743038981702466</v>
+        <v>-0.2490055688146381</v>
       </c>
       <c r="G3" t="n">
-        <v>5.872499166598002e-24</v>
+        <v>7.850666033319035e-24</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,16 +549,16 @@
         <v>84</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1726190476190476</v>
+        <v>0.02465986394557824</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4940476190476191</v>
+        <v>-0.07057823129251702</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6666666666666667</v>
+        <v>-0.09523809523809526</v>
       </c>
       <c r="G4" t="n">
-        <v>0.667781101001432</v>
+        <v>0.6469013854703428</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -577,16 +577,16 @@
         <v>208</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7259615384615384</v>
+        <v>0.1037087912087912</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3894230769230769</v>
+        <v>-0.05563186813186814</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.115384615384615</v>
+        <v>-0.1593406593406594</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01738265019930525</v>
+        <v>0.01193312454086841</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -609,16 +609,16 @@
         <v>212</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8066037735849056</v>
+        <v>0.1152291105121294</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2924528301886792</v>
+        <v>-0.04177897574123988</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.099056603773585</v>
+        <v>-0.1570080862533693</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01021221424803583</v>
+        <v>0.01500048503827648</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -641,16 +641,16 @@
         <v>185</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5567567567567567</v>
+        <v>0.07953667953667955</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6162162162162163</v>
+        <v>-0.08803088803088803</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.172972972972973</v>
+        <v>-0.1675675675675676</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002279928561499132</v>
+        <v>0.001857920401686629</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
